--- a/tests/fixtures/browser/spike/minute-power-ooxml.xlsx
+++ b/tests/fixtures/browser/spike/minute-power-ooxml.xlsx
@@ -1,6 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <bookViews>
+    <workbookView activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet name="功率预测" sheetId="1" r:id="rId1"/>
     <sheet name="Cover" sheetId="2" r:id="rId2"/>
@@ -276,7 +279,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>cover</t>
+          <t xml:space="preserve">cover</t>
         </is>
       </c>
     </row>
